--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_36.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_36.xlsx
@@ -471,127 +471,127 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>34566</v>
+        <v>58745</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luna Fernandes</t>
+          <t>Gabriel Cavalcanti</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45098</v>
+        <v>45097</v>
       </c>
       <c r="G2" t="n">
-        <v>6848.45</v>
+        <v>7501.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17227</v>
+        <v>44639</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alexia Carvalho</t>
+          <t>Carolina Freitas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45078</v>
+        <v>45096</v>
       </c>
       <c r="G3" t="n">
-        <v>6885.77</v>
+        <v>3503.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84874</v>
+        <v>35828</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gabriela Duarte</t>
+          <t>Sabrina da Paz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45094</v>
+        <v>45089</v>
       </c>
       <c r="G4" t="n">
-        <v>8466.790000000001</v>
+        <v>8353.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54966</v>
+        <v>56000</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcela Rodrigues</t>
+          <t>Igor Vieira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45078</v>
+        <v>45101</v>
       </c>
       <c r="G5" t="n">
-        <v>5008.53</v>
+        <v>8823.370000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35458</v>
+        <v>6152</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clarice Martins</t>
+          <t>Emilly Pires</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,89 +601,89 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45085</v>
+        <v>45096</v>
       </c>
       <c r="G6" t="n">
-        <v>10084.74</v>
+        <v>8124.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24441</v>
+        <v>29245</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Srta. Maria Clara da Rocha</t>
+          <t>Ana Carolina Cardoso</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45085</v>
+        <v>45091</v>
       </c>
       <c r="G7" t="n">
-        <v>8489.98</v>
+        <v>4087.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64841</v>
+        <v>65637</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paulo Caldeira</t>
+          <t>Caroline Santos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45082</v>
+        <v>45104</v>
       </c>
       <c r="G8" t="n">
-        <v>3659.1</v>
+        <v>7721.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11190</v>
+        <v>39456</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Milena Porto</t>
+          <t>Maria Julia Dias</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -692,71 +692,71 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45081</v>
+        <v>45101</v>
       </c>
       <c r="G9" t="n">
-        <v>9206.870000000001</v>
+        <v>9989.940000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99195</v>
+        <v>23363</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luana Fogaça</t>
+          <t>Bruno Lima</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45078</v>
+        <v>45103</v>
       </c>
       <c r="G10" t="n">
-        <v>6133.81</v>
+        <v>12080.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12358</v>
+        <v>4731</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sabrina Lopes</t>
+          <t>Kamilly da Cunha</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45081</v>
+        <v>45097</v>
       </c>
       <c r="G11" t="n">
-        <v>10099.9</v>
+        <v>3102.89</v>
       </c>
     </row>
   </sheetData>
